--- a/resources/templates/standard/B2100-11.xlsx
+++ b/resources/templates/standard/B2100-11.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>▣ 고객사 불량 유효성 검증 관리대장 (0000년)</t>
   </si>
@@ -1290,11 +1293,13 @@
   </cols>
   <sheetData>
     <row r="1" ht="17.5" customHeight="1" spans="1:250" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -1311,18 +1316,18 @@
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
       <c r="S1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U1" s="4"/>
       <c r="V1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W1" s="4"/>
       <c r="X1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y1" s="4"/>
       <c r="Z1" s="5"/>
@@ -2309,7 +2314,7 @@
     </row>
     <row r="5" ht="20.15" customHeight="1" spans="1:250" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
@@ -2563,20 +2568,20 @@
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:250" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" s="13"/>
       <c r="G6" s="13"/>
       <c r="H6" s="13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I6" s="13"/>
       <c r="J6" s="13"/>
@@ -2588,7 +2593,7 @@
       <c r="P6" s="13"/>
       <c r="Q6" s="13"/>
       <c r="R6" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S6" s="13"/>
       <c r="T6" s="13"/>
@@ -3833,51 +3838,51 @@
     </row>
     <row r="11" ht="37.15" customHeight="1" spans="1:250" x14ac:dyDescent="0.25">
       <c r="A11" s="23" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F11" s="27"/>
       <c r="G11" s="27"/>
       <c r="H11" s="27"/>
       <c r="I11" s="27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J11" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K11" s="28"/>
       <c r="L11" s="28"/>
       <c r="M11" s="28"/>
       <c r="N11" s="29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O11" s="29"/>
       <c r="P11" s="30" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q11" s="30"/>
       <c r="R11" s="30"/>
       <c r="S11" s="30"/>
       <c r="T11" s="30"/>
       <c r="U11" s="30" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V11" s="30"/>
       <c r="W11" s="30"/>
       <c r="X11" s="30"/>
       <c r="Y11" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z11" s="5"/>
       <c r="AA11" s="5"/>
@@ -4111,61 +4116,61 @@
       <c r="C12" s="25"/>
       <c r="D12" s="26"/>
       <c r="E12" s="32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F12" s="33" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G12" s="33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H12" s="33" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I12" s="32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J12" s="32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K12" s="33" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L12" s="32" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M12" s="32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N12" s="34" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O12" s="34" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P12" s="35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q12" s="34" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R12" s="34" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S12" s="34" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T12" s="34" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U12" s="36" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V12" s="36" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="W12" s="35" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="X12" s="35"/>
       <c r="Y12" s="31"/>
